--- a/sources/sources.xlsx
+++ b/sources/sources.xlsx
@@ -2622,7 +2622,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>listing page yields no links to our parser; ReliefWeb's API needs an approved appname (checked 11 Aug 2026)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sources/sources.xlsx
+++ b/sources/sources.xlsx
@@ -1926,12 +1926,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>EXAMPLE — delete this row</t>
+          <t>Jaap van Hierden</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Resident Coordinator</t>
+          <t>UN Resident Coordinator</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Ж. Смит, Smith Jane, J. Smith</t>
+          <t>Яап ван Хиердэн, ван Хиердэн, Jaap Van Hierden</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1951,27 +1951,31 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>How a row should look</t>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages; RC since 1 Jan 2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Beate Dastel</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>UN Resident Coordinator</t>
+          <t>UNICEF Representative</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>UNRCO</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Беате Дастел, Дастел</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1979,225 +1983,297 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Add the real name and every Cyrillic spelling</t>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages; took office Feb 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Lionel Laurens</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Head of Office</t>
+          <t>UNDP Resident Representative</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>UNICEF</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
+          <t>UNDP</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Лионель Лоуренс, Лионел Лорон, Лоуренс</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages; press spelling from mnb.mn 5 Aug 2026 differs from the UN site</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Socorro Escalante</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Head of Office</t>
+          <t>WHO Representative</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>UNDP</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
+          <t>WHO</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Сокорро Эскалантэ, Эскалантэ</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Yoko Fujimura</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Head of Office</t>
+          <t>IOM Chief of Mission</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>UNFPA</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
+          <t>IOM</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Ёко Фүжимүра, Фүжимүра</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Qingyun Diao</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>FAO Representative</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>WHO</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
+          <t>FAO</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Чинюнь Дяо, Дяо</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Khalid Sharifi</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Head of Office</t>
+          <t>UNFPA Head of Office</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>IOM</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
+          <t>UNFPA</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Халид Шарифи, Шарифи</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Ganbold Baasanjav</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Head, ESCAP East and North-East Asia Office</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>FAO</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
+          <t>ESCAP</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Ганболд Баасанжав, Б.Ганболд</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Doljinsuren Jambal</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Head of Office</t>
+          <t>Head of the Resident Coordinator's Office</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>UNESCO</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
+          <t>UNRCO</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Должинсүрэн Жамбал, Ж.Должинсүрэн</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Altangerel Choijoo</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Head of Office</t>
+          <t>National Human Rights Advisor</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
+          <t>UNRCO</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Алтангэрэл Чойжоо, Ч.Алтангэрэл</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>&lt;FILL IN&gt;</t>
+          <t>Soyolmaa Dolgor</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Head of Office</t>
+          <t>Development Coordination Officer, Communications</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>UN Women</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
+          <t>UNRCO</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Соёлмаа Долгор, Д.Соёлмаа</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>verified 11 Aug 2026 from mongolia.un.org team pages</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sources/sources.xlsx
+++ b/sources/sources.xlsx
@@ -1973,7 +1973,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Беате Дастел, Дастел</t>
+          <t>Беате Дастел</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Лионель Лоуренс, Лионел Лорон, Лоуренс</t>
+          <t>Лионель Лоуренс, Лионел Лорон</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Сокорро Эскалантэ, Эскалантэ</t>
+          <t>Сокорро Эскалантэ</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Ёко Фүжимүра, Фүжимүра</t>
+          <t>Ёко Фүжимүра</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Чинюнь Дяо, Дяо</t>
+          <t>Чинюнь Дяо</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Халид Шарифи, Шарифи</t>
+          <t>Халид Шарифи</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">

--- a/sources/sources.xlsx
+++ b/sources/sources.xlsx
@@ -2695,12 +2695,12 @@
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>listing page yields no links to our parser; ReliefWeb's API needs an approved appname (checked 11 Aug 2026)</t>
+          <t>off: listing page exposes no links to our parser and the ReliefWeb API needs an approved appname (11 Aug 2026). Set active=yes if we register.</t>
         </is>
       </c>
     </row>
